--- a/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
+++ b/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammed.shurafa\ArcGIS\My Survey Designs\IND-Damage Assessment of Damaged Industrial Facilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021BC7E8-E23A-4DBF-B352-1CD68703C43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC18321-C210-4CC3-ADD3-4B4BF3C4954D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="537" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7096,6 +7096,9 @@
       <c r="C107" s="30" t="s">
         <v>1560</v>
       </c>
+      <c r="F107" s="31">
+        <v>1</v>
+      </c>
       <c r="M107" s="31" t="s">
         <v>1521</v>
       </c>

--- a/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
+++ b/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammed.shurafa\ArcGIS\My Survey Designs\IND-Damage Assessment of Damaged Industrial Facilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0808537-6934-45DE-A791-FCE2FAA11DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9B6378-2D6C-4BCA-97CE-C4FA312C1E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="537" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="1576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="1576">
   <si>
     <t>type</t>
   </si>
@@ -6040,9 +6040,6 @@
       <c r="D36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K36" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6060,9 +6057,6 @@
       <c r="D37" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K37" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6077,9 +6071,6 @@
       <c r="C38" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K38" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6109,9 +6100,6 @@
       <c r="I39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K39" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6141,9 +6129,6 @@
       <c r="I40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K40" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6161,9 +6146,6 @@
       <c r="C41" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K41" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6178,9 +6160,6 @@
       <c r="C42" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K42" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6218,9 +6197,6 @@
       <c r="D44" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K44" s="1" t="s">
         <v>1461</v>
       </c>
@@ -6255,9 +6231,6 @@
       <c r="C46" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K46" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10095,9 +10068,6 @@
       <c r="C291" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="J291" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K291" s="1" t="s">
         <v>1523</v>
       </c>
@@ -10112,9 +10082,6 @@
       <c r="C292" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="J292" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="O292" s="1" t="s">
         <v>1237</v>
       </c>
@@ -10129,9 +10096,6 @@
       <c r="C293" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="J293" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K293" s="1" t="s">
         <v>1523</v>
       </c>
@@ -10146,9 +10110,6 @@
       <c r="C294" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="J294" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K294" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10166,9 +10127,6 @@
       <c r="C295" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="J295" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="O295" s="1" t="s">
         <v>1238</v>
       </c>
@@ -10340,9 +10298,6 @@
       <c r="C308" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="J308" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K308" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10357,9 +10312,6 @@
       <c r="C309" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="J309" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K309" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10374,9 +10326,6 @@
       <c r="C310" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="J310" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K310" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10391,9 +10340,6 @@
       <c r="C311" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="J311" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K311" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10408,9 +10354,6 @@
       <c r="C312" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="J312" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K312" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10425,9 +10368,6 @@
       <c r="C313" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="J313" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K313" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10442,9 +10382,6 @@
       <c r="C314" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="J314" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K314" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10500,9 +10437,6 @@
       <c r="C318" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J318" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K318" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10520,9 +10454,6 @@
       <c r="C319" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="J319" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K319" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10537,9 +10468,6 @@
       <c r="C320" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="J320" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K320" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10554,9 +10482,6 @@
       <c r="C321" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="J321" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K321" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10571,9 +10496,6 @@
       <c r="C322" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="J322" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="O322" s="1" t="s">
         <v>1239</v>
       </c>
@@ -10615,9 +10537,6 @@
       <c r="C325" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="J325" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K325" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10632,9 +10551,6 @@
       <c r="C326" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="J326" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K326" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10652,9 +10568,6 @@
       <c r="D327" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J327" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K327" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10672,9 +10585,6 @@
       <c r="D328" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J328" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K328" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10726,9 +10636,6 @@
       <c r="I331" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J331" s="1" t="s">
-        <v>1481</v>
-      </c>
     </row>
     <row r="332" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="15" t="s">
@@ -10749,9 +10656,6 @@
       <c r="I332" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J332" s="1" t="s">
-        <v>1481</v>
-      </c>
     </row>
     <row r="333" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="15" t="s">
@@ -10772,9 +10676,6 @@
       <c r="I333" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J333" s="1" t="s">
-        <v>1481</v>
-      </c>
     </row>
     <row r="334" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="15" t="s">
@@ -10795,9 +10696,6 @@
       <c r="I334" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J334" s="1" t="s">
-        <v>1481</v>
-      </c>
     </row>
     <row r="335" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="15" t="s">
@@ -10818,9 +10716,6 @@
       <c r="I335" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J335" s="1" t="s">
-        <v>1481</v>
-      </c>
     </row>
     <row r="336" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="15" t="s">
@@ -10846,9 +10741,6 @@
       <c r="C337" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="J337" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K337" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10863,9 +10755,6 @@
       <c r="C338" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="J338" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K338" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10880,9 +10769,6 @@
       <c r="C339" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="J339" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K339" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10897,9 +10783,6 @@
       <c r="C340" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="J340" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K340" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10914,9 +10797,6 @@
       <c r="C341" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="J341" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K341" s="1" t="s">
         <v>1461</v>
       </c>
@@ -10996,9 +10876,6 @@
       <c r="C347" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="J347" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="K347" s="1" t="s">
         <v>1461</v>
       </c>
@@ -11012,9 +10889,6 @@
       </c>
       <c r="C348" s="15" t="s">
         <v>290</v>
-      </c>
-      <c r="J348" s="1" t="s">
-        <v>1481</v>
       </c>
       <c r="K348" s="1" t="s">
         <v>1461</v>

--- a/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
+++ b/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammed.shurafa\ArcGIS\My Survey Designs\IND-Damage Assessment of Damaged Industrial Facilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9B6378-2D6C-4BCA-97CE-C4FA312C1E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D30A01E-CACD-4BE8-91D4-A54013D729C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="537" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="1576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3356" uniqueCount="1576">
   <si>
     <t>type</t>
   </si>
@@ -5838,6 +5838,9 @@
       <c r="I26" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="J26" s="1" t="s">
+        <v>1481</v>
+      </c>
       <c r="K26" s="1" t="s">
         <v>1331</v>
       </c>
@@ -5884,6 +5887,9 @@
       <c r="D28" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="J28" s="1" t="s">
+        <v>1481</v>
+      </c>
       <c r="K28" s="1" t="s">
         <v>1331</v>
       </c>
@@ -5930,6 +5936,9 @@
       <c r="I30" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="J30" s="1" t="s">
+        <v>1481</v>
+      </c>
       <c r="K30" s="1" t="s">
         <v>1331</v>
       </c>
@@ -5953,6 +5962,9 @@
       <c r="I31" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="J31" s="1" t="s">
+        <v>1481</v>
+      </c>
       <c r="K31" s="1" t="s">
         <v>1331</v>
       </c>
@@ -5972,6 +5984,9 @@
       </c>
       <c r="F32" s="1" t="s">
         <v>1325</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>1481</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>1331</v>

--- a/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
+++ b/IND-Damage Assessment of Damaged Industrial Facilities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammed.shurafa\ArcGIS\My Survey Designs\IND-Damage Assessment of Damaged Industrial Facilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC203EFF-452F-4C59-A3FB-79EFB38841CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD666D0-3D8A-43CB-8682-FB1C2A8F1ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="537" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$A$1:$W$413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$A$1:$W$414</definedName>
     <definedName name="aGrp">#REF!</definedName>
     <definedName name="aRank">#REF!</definedName>
     <definedName name="aRpt">#REF!</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="1588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="1591">
   <si>
     <t>type</t>
   </si>
@@ -4833,6 +4833,15 @@
   </si>
   <si>
     <t>Location_Is_Red</t>
+  </si>
+  <si>
+    <t>31.30776877303826 34.21987659623359</t>
+  </si>
+  <si>
+    <t>Location_Is_Default</t>
+  </si>
+  <si>
+    <t>if(string(${Location_On_Map}) = '31.30776877303826 34.21987659623359', 1, 0)</t>
   </si>
 </sst>
 </file>
@@ -5371,7 +5380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X413"/>
+  <dimension ref="A1:X414"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="31.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44" style="15" customWidth="1"/>
@@ -5379,7 +5388,7 @@
     <col min="3" max="3" width="48.140625" style="15" customWidth="1"/>
     <col min="4" max="4" width="29.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="39.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" customWidth="1"/>
     <col min="8" max="8" width="65.85546875" style="1" customWidth="1"/>
     <col min="9" max="9" width="89.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -7335,7 +7344,7 @@
         <v>1227</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1310</v>
+        <v>1588</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>127</v>
@@ -7348,37 +7357,31 @@
       </c>
     </row>
     <row r="119" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B119" s="15" t="s">
-        <v>867</v>
-      </c>
-      <c r="C119" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>1542</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>1540</v>
+      <c r="A119" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1589</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>1590</v>
       </c>
     </row>
     <row r="120" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="15" t="s">
-        <v>1088</v>
+        <v>17</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K120" s="1" t="s">
         <v>1542</v>
@@ -7389,16 +7392,16 @@
     </row>
     <row r="121" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="15" t="s">
-        <v>1191</v>
+        <v>1088</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K121" s="1" t="s">
         <v>1542</v>
@@ -7406,22 +7409,19 @@
       <c r="L121" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="M121" s="1" t="s">
-        <v>1038</v>
-      </c>
     </row>
     <row r="122" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="15" t="s">
-        <v>1090</v>
+        <v>1191</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K122" s="1" t="s">
         <v>1542</v>
@@ -7430,18 +7430,18 @@
         <v>1540</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="123" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="15" t="s">
-        <v>1192</v>
+        <v>1090</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>1204</v>
+        <v>870</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>94</v>
@@ -7453,18 +7453,18 @@
         <v>1540</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="124" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="15" t="s">
-        <v>1093</v>
+        <v>1192</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>871</v>
+        <v>1204</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>94</v>
@@ -7476,18 +7476,18 @@
         <v>1540</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="125" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="15" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>94</v>
@@ -7499,18 +7499,18 @@
         <v>1540</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="126" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="15" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>94</v>
@@ -7522,21 +7522,21 @@
         <v>1540</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="127" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="15" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K127" s="1" t="s">
         <v>1542</v>
@@ -7545,21 +7545,21 @@
         <v>1540</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="128" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="15" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K128" s="1" t="s">
         <v>1542</v>
@@ -7568,18 +7568,18 @@
         <v>1540</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>1276</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="15" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>94</v>
@@ -7591,18 +7591,18 @@
         <v>1540</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="15" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>94</v>
@@ -7614,18 +7614,18 @@
         <v>1540</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="15" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>94</v>
@@ -7637,21 +7637,21 @@
         <v>1540</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="15" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>1542</v>
@@ -7660,21 +7660,21 @@
         <v>1540</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>1040</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="15" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K133" s="1" t="s">
         <v>1542</v>
@@ -7683,18 +7683,18 @@
         <v>1540</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="15" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>94</v>
@@ -7706,18 +7706,18 @@
         <v>1540</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="15" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>1205</v>
+        <v>881</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>94</v>
@@ -7729,18 +7729,18 @@
         <v>1540</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="15" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>882</v>
+        <v>1205</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>94</v>
@@ -7752,18 +7752,18 @@
         <v>1540</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="15" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>94</v>
@@ -7775,18 +7775,18 @@
         <v>1540</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="15" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>94</v>
@@ -7798,18 +7798,18 @@
         <v>1540</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="15" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>94</v>
@@ -7821,18 +7821,18 @@
         <v>1540</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="15" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>94</v>
@@ -7844,21 +7844,21 @@
         <v>1540</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="15" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K141" s="1" t="s">
         <v>1542</v>
@@ -7867,21 +7867,21 @@
         <v>1540</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>1041</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>1542</v>
@@ -7890,18 +7890,18 @@
         <v>1540</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="15" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>94</v>
@@ -7913,18 +7913,18 @@
         <v>1540</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="15" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>1206</v>
+        <v>889</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>94</v>
@@ -7936,18 +7936,18 @@
         <v>1540</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="15" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>94</v>
@@ -7959,18 +7959,18 @@
         <v>1540</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="15" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>94</v>
@@ -7982,18 +7982,18 @@
         <v>1540</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="15" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>94</v>
@@ -8005,18 +8005,18 @@
         <v>1540</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="15" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>94</v>
@@ -8028,18 +8028,18 @@
         <v>1540</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="15" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>94</v>
@@ -8051,21 +8051,21 @@
         <v>1540</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="15" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>892</v>
+        <v>1211</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K150" s="1" t="s">
         <v>1542</v>
@@ -8074,21 +8074,21 @@
         <v>1540</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>1042</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="15" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K151" s="1" t="s">
         <v>1542</v>
@@ -8097,18 +8097,18 @@
         <v>1540</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>1280</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="15" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>94</v>
@@ -8120,18 +8120,18 @@
         <v>1540</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="15" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>94</v>
@@ -8143,18 +8143,18 @@
         <v>1540</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="15" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>94</v>
@@ -8166,38 +8166,41 @@
         <v>1540</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="15" t="s">
-        <v>10</v>
+        <v>1153</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>125</v>
+        <v>117</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>1542</v>
       </c>
       <c r="L155" s="1" t="s">
         <v>1540</v>
       </c>
+      <c r="M155" s="1" t="s">
+        <v>1283</v>
+      </c>
     </row>
     <row r="156" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="15" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>1542</v>
+        <v>125</v>
       </c>
       <c r="L156" s="1" t="s">
         <v>1540</v>
@@ -8205,16 +8208,16 @@
     </row>
     <row r="157" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="15" t="s">
-        <v>1155</v>
+        <v>17</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>1542</v>
@@ -8225,13 +8228,13 @@
     </row>
     <row r="158" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="15" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>41</v>
@@ -8245,16 +8248,16 @@
     </row>
     <row r="159" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="15" t="s">
-        <v>40</v>
+        <v>1157</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>1198</v>
+        <v>897</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>1542</v>
@@ -8268,13 +8271,13 @@
         <v>40</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>1542</v>
@@ -8285,13 +8288,16 @@
     </row>
     <row r="161" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="15" t="s">
-        <v>1159</v>
+        <v>40</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>898</v>
+        <v>1199</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>1542</v>
@@ -8302,13 +8308,13 @@
     </row>
     <row r="162" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="15" t="s">
-        <v>17</v>
+        <v>1159</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>1542</v>
@@ -8316,19 +8322,16 @@
       <c r="L162" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="M162" s="1" t="s">
-        <v>1064</v>
-      </c>
     </row>
     <row r="163" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="15" t="s">
-        <v>1161</v>
+        <v>17</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K163" s="1" t="s">
         <v>1542</v>
@@ -8336,140 +8339,137 @@
       <c r="L163" s="1" t="s">
         <v>1540</v>
       </c>
-    </row>
-    <row r="164" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="16" t="s">
+      <c r="M163" s="1" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="15" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B164" s="15" t="s">
+        <v>900</v>
+      </c>
+      <c r="C164" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B164" s="16" t="s">
+      <c r="B165" s="16" t="s">
         <v>1350</v>
       </c>
-      <c r="C164" s="22" t="s">
+      <c r="C165" s="22" t="s">
         <v>1359</v>
       </c>
-      <c r="G164" s="6"/>
-      <c r="L164" s="3" t="s">
+      <c r="G165" s="6"/>
+      <c r="L165" s="3" t="s">
         <v>1541</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B165" s="15" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C165" s="20" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="15" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B166" s="15" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C166" s="20" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B166" s="15" t="s">
+      <c r="B167" s="15" t="s">
         <v>1352</v>
       </c>
-      <c r="C166" s="15" t="s">
+      <c r="C167" s="15" t="s">
         <v>1361</v>
       </c>
-      <c r="L166" s="1" t="s">
+      <c r="L167" s="1" t="s">
         <v>1353</v>
       </c>
     </row>
-    <row r="167" spans="1:13" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="18" t="s">
+    <row r="168" spans="1:13" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B167" s="21"/>
-      <c r="C167" s="21"/>
-    </row>
-    <row r="168" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B168" s="15" t="s">
-        <v>901</v>
-      </c>
-      <c r="C168" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="K168" s="1" t="s">
-        <v>1542</v>
-      </c>
-      <c r="L168" s="1" t="s">
-        <v>1540</v>
-      </c>
-      <c r="M168" s="1" t="s">
-        <v>1065</v>
-      </c>
+      <c r="B168" s="21"/>
+      <c r="C168" s="21"/>
     </row>
     <row r="169" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="15" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>1390</v>
+        <v>139</v>
+      </c>
+      <c r="K169" s="1" t="s">
+        <v>1542</v>
       </c>
       <c r="L169" s="1" t="s">
         <v>1540</v>
       </c>
       <c r="M169" s="1" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B170" s="15" t="s">
+        <v>902</v>
+      </c>
+      <c r="C170" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="L170" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="M170" s="1" t="s">
         <v>1066</v>
       </c>
     </row>
-    <row r="170" spans="1:13" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="16" t="s">
+    <row r="171" spans="1:13" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B170" s="16" t="s">
+      <c r="B171" s="16" t="s">
         <v>816</v>
       </c>
-      <c r="C170" s="16" t="s">
+      <c r="C171" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="M170" s="6" t="s">
+      <c r="M171" s="6" t="s">
         <v>1067</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B171" s="24" t="s">
-        <v>905</v>
-      </c>
-      <c r="C171" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="K171" s="1" t="s">
-        <v>1542</v>
-      </c>
-      <c r="L171" s="1" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="15" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B172" s="24" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="H172" s="1" t="s">
-        <v>1468</v>
-      </c>
-      <c r="I172" s="1" t="s">
-        <v>1469</v>
+        <v>142</v>
       </c>
       <c r="K172" s="1" t="s">
         <v>1542</v>
@@ -8483,10 +8483,16 @@
         <v>40</v>
       </c>
       <c r="B173" s="24" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>1469</v>
       </c>
       <c r="K173" s="1" t="s">
         <v>1542</v>
@@ -8500,10 +8506,10 @@
         <v>40</v>
       </c>
       <c r="B174" s="24" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>1470</v>
+        <v>144</v>
       </c>
       <c r="K174" s="1" t="s">
         <v>1542</v>
@@ -8514,13 +8520,13 @@
     </row>
     <row r="175" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="15" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="B175" s="24" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>146</v>
+        <v>1470</v>
       </c>
       <c r="K175" s="1" t="s">
         <v>1542</v>
@@ -8529,87 +8535,87 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="176" spans="1:13" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="18" t="s">
+    <row r="176" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B176" s="24" t="s">
+        <v>909</v>
+      </c>
+      <c r="C176" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K176" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L176" s="1" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B176" s="21"/>
-      <c r="C176" s="21"/>
-    </row>
-    <row r="177" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15" t="s">
+      <c r="B177" s="21"/>
+      <c r="C177" s="21"/>
+    </row>
+    <row r="178" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B177" s="24" t="s">
+      <c r="B178" s="24" t="s">
         <v>913</v>
       </c>
-      <c r="C177" s="15" t="s">
+      <c r="C178" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="K177" s="1" t="s">
+      <c r="K178" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="L177" s="1" t="s">
+      <c r="L178" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="M177" s="1" t="s">
+      <c r="M178" s="1" t="s">
         <v>1066</v>
       </c>
     </row>
-    <row r="178" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="26" t="s">
+    <row r="179" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B178" s="26" t="s">
+      <c r="B179" s="26" t="s">
         <v>1237</v>
       </c>
-      <c r="C178" s="26" t="s">
+      <c r="C179" s="26" t="s">
         <v>1414</v>
       </c>
-      <c r="L178" s="8" t="s">
+      <c r="L179" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T178" s="8" t="s">
+      <c r="T179" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="179" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B179" s="15" t="s">
-        <v>915</v>
-      </c>
-      <c r="C179" s="15" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="180" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="15" t="s">
-        <v>1230</v>
+        <v>10</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>1234</v>
+        <v>915</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>1236</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="181" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="15" t="s">
-        <v>28</v>
+        <v>1230</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>914</v>
+        <v>1234</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>1514</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="N181" s="1" t="s">
-        <v>150</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="182" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8617,54 +8623,60 @@
         <v>28</v>
       </c>
       <c r="B182" s="15" t="s">
+        <v>914</v>
+      </c>
+      <c r="C182" s="15" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="N182" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B183" s="15" t="s">
         <v>1235</v>
       </c>
-      <c r="C182" s="15" t="s">
+      <c r="C183" s="15" t="s">
         <v>1413</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="D183" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G182" s="1" t="s">
+      <c r="G183" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="N182" s="1" t="s">
+      <c r="N183" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="183" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B183" s="26"/>
-      <c r="C183" s="26"/>
     </row>
     <row r="184" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+    </row>
+    <row r="185" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B184" s="26" t="s">
+      <c r="B185" s="26" t="s">
         <v>1272</v>
       </c>
-      <c r="C184" s="26" t="s">
+      <c r="C185" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="L184" s="8" t="s">
+      <c r="L185" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T184" s="8" t="s">
+      <c r="T185" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="185" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B185" s="15" t="s">
-        <v>916</v>
-      </c>
-      <c r="C185" s="15" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="186" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8672,66 +8684,66 @@
         <v>10</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>1404</v>
+        <v>154</v>
       </c>
     </row>
     <row r="187" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="15" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>1193</v>
+        <v>917</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="K187" s="1" t="s">
-        <v>1542</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="188" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B188" s="15" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C188" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B188" s="15" t="s">
+      <c r="B189" s="15" t="s">
         <v>1516</v>
       </c>
-      <c r="C188" s="15" t="s">
+      <c r="C189" s="15" t="s">
         <v>1515</v>
       </c>
-      <c r="R188" s="1" t="s">
+      <c r="R189" s="1" t="s">
         <v>1310</v>
       </c>
     </row>
-    <row r="189" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="26" t="s">
+    <row r="190" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B189" s="26" t="s">
+      <c r="B190" s="26" t="s">
         <v>1273</v>
       </c>
-      <c r="C189" s="26" t="s">
+      <c r="C190" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="L189" s="8" t="s">
+      <c r="L190" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T189" s="8" t="s">
+      <c r="T190" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="190" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B190" s="15" t="s">
-        <v>918</v>
-      </c>
-      <c r="C190" s="15" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="191" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8739,24 +8751,21 @@
         <v>10</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>1409</v>
+        <v>157</v>
       </c>
     </row>
     <row r="192" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="15" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B192" s="15" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="K192" s="1" t="s">
-        <v>1542</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="193" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8764,10 +8773,10 @@
         <v>17</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K193" s="1" t="s">
         <v>1542</v>
@@ -8775,13 +8784,16 @@
     </row>
     <row r="194" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="15" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
+      </c>
+      <c r="K194" s="1" t="s">
+        <v>1542</v>
       </c>
     </row>
     <row r="195" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8789,166 +8801,163 @@
         <v>40</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="K195" s="1" t="s">
-        <v>1542</v>
+        <v>160</v>
       </c>
     </row>
     <row r="196" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="15" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>163</v>
+        <v>923</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="O196" s="1" t="s">
-        <v>1215</v>
+        <v>161</v>
+      </c>
+      <c r="K196" s="1" t="s">
+        <v>1542</v>
       </c>
     </row>
     <row r="197" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="15" t="s">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>924</v>
+        <v>163</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
+      </c>
+      <c r="O197" s="1" t="s">
+        <v>1215</v>
       </c>
     </row>
     <row r="198" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="15" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>9</v>
+        <v>924</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="O198" s="1" t="s">
-        <v>1216</v>
+        <v>164</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="15" t="s">
-        <v>1164</v>
+        <v>162</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>925</v>
+        <v>9</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="K199" s="1" t="s">
-        <v>1542</v>
+        <v>9</v>
+      </c>
+      <c r="O199" s="1" t="s">
+        <v>1216</v>
       </c>
     </row>
     <row r="200" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="15" t="s">
-        <v>1077</v>
+        <v>1164</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C200" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="M200"/>
-      <c r="T200" s="1" t="s">
-        <v>1459</v>
+        <v>166</v>
+      </c>
+      <c r="K200" s="1" t="s">
+        <v>1542</v>
       </c>
     </row>
     <row r="201" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="15" t="s">
-        <v>40</v>
+        <v>1077</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C201" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D201" s="27" t="s">
-        <v>1529</v>
-      </c>
-      <c r="K201" s="1" t="s">
-        <v>1544</v>
-      </c>
-      <c r="L201" t="s">
-        <v>1522</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="M201"/>
       <c r="T201" s="1" t="s">
         <v>1459</v>
       </c>
     </row>
     <row r="202" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="15" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>169</v>
+        <v>927</v>
       </c>
       <c r="C202" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="O202" s="1" t="s">
-        <v>1217</v>
+        <v>168</v>
+      </c>
+      <c r="D202" s="27" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K202" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="L202" t="s">
+        <v>1522</v>
+      </c>
+      <c r="T202" s="1" t="s">
+        <v>1459</v>
       </c>
     </row>
     <row r="203" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="15" t="s">
-        <v>1166</v>
+        <v>162</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>928</v>
+        <v>169</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
+      </c>
+      <c r="O203" s="1" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="204" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="15" t="s">
-        <v>40</v>
+        <v>1166</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C204" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K204" s="1" t="s">
-        <v>1542</v>
+        <v>171</v>
       </c>
     </row>
     <row r="205" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="15" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>174</v>
+        <v>929</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="O205" s="1" t="s">
-        <v>1218</v>
+        <v>172</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K205" s="1" t="s">
+        <v>1542</v>
       </c>
     </row>
     <row r="206" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8956,13 +8965,13 @@
         <v>162</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>176</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="207" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8970,13 +8979,13 @@
         <v>162</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C207" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="208" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8984,123 +8993,120 @@
         <v>162</v>
       </c>
       <c r="B208" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C208" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="O208" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B209" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C208" s="15" t="s">
+      <c r="C209" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="O208" s="1" t="s">
+      <c r="O209" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="209" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="16" t="s">
+    <row r="210" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B209" s="16" t="s">
+      <c r="B210" s="16" t="s">
         <v>1354</v>
       </c>
-      <c r="C209" s="22" t="s">
+      <c r="C210" s="22" t="s">
         <v>1355</v>
       </c>
-      <c r="G209" s="6"/>
-      <c r="L209" s="3" t="s">
+      <c r="G210" s="6"/>
+      <c r="L210" s="3" t="s">
         <v>1541</v>
-      </c>
-    </row>
-    <row r="210" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="15" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B210" s="15" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C210" s="20" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="211" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="15" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B211" s="15" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C211" s="20" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="212" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B211" s="15" t="s">
+      <c r="B212" s="15" t="s">
         <v>1357</v>
       </c>
-      <c r="C211" s="15" t="s">
+      <c r="C212" s="15" t="s">
         <v>1370</v>
       </c>
-      <c r="L211" s="1" t="s">
+      <c r="L212" s="1" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="212" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="18" t="s">
+    <row r="213" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B212" s="21"/>
-      <c r="C212" s="21"/>
-    </row>
-    <row r="213" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B213" s="26"/>
-      <c r="C213" s="26"/>
+      <c r="B213" s="21"/>
+      <c r="C213" s="21"/>
     </row>
     <row r="214" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B214" s="26"/>
+      <c r="C214" s="26"/>
+    </row>
+    <row r="215" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B214" s="26" t="s">
+      <c r="B215" s="26" t="s">
         <v>1262</v>
       </c>
-      <c r="C214" s="26" t="s">
+      <c r="C215" s="26" t="s">
         <v>1265</v>
       </c>
-      <c r="L214" s="8" t="s">
+      <c r="L215" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T214" s="8" t="s">
+      <c r="T215" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="215" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B215" s="15" t="s">
-        <v>930</v>
-      </c>
-      <c r="C215" s="15" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="216" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="15" t="s">
-        <v>1230</v>
+        <v>10</v>
       </c>
       <c r="B216" s="15" t="s">
-        <v>1240</v>
+        <v>930</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>1412</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="217" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="15" t="s">
-        <v>28</v>
+        <v>1230</v>
       </c>
       <c r="B217" s="15" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>1517</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="N217" s="1" t="s">
-        <v>150</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="218" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9108,24 +9114,34 @@
         <v>28</v>
       </c>
       <c r="B218" s="15" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C218" s="15" t="s">
+        <v>1517</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="N218" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B219" s="15" t="s">
         <v>1239</v>
       </c>
-      <c r="C218" s="15" t="s">
+      <c r="C219" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="G218" s="1" t="s">
+      <c r="G219" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="N218" s="1" t="s">
+      <c r="N219" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="219" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
     </row>
     <row r="220" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="26" t="s">
@@ -9136,30 +9152,26 @@
     </row>
     <row r="221" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B221" s="26"/>
+      <c r="C221" s="26"/>
+    </row>
+    <row r="222" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B221" s="26" t="s">
+      <c r="B222" s="26" t="s">
         <v>817</v>
       </c>
-      <c r="C221" s="26" t="s">
+      <c r="C222" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="L221" s="8" t="s">
+      <c r="L222" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T221" s="8" t="s">
+      <c r="T222" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="222" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B222" s="15" t="s">
-        <v>931</v>
-      </c>
-      <c r="C222" s="15" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="223" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9167,209 +9179,203 @@
         <v>10</v>
       </c>
       <c r="B223" s="15" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C223" s="15" t="s">
-        <v>1405</v>
+        <v>183</v>
       </c>
     </row>
     <row r="224" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="15" t="s">
-        <v>1168</v>
+        <v>10</v>
       </c>
       <c r="B224" s="15" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C224" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K224" s="1" t="s">
-        <v>1542</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="225" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="15" t="s">
-        <v>17</v>
+        <v>1168</v>
       </c>
       <c r="B225" s="15" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="D225" s="27" t="s">
-        <v>1530</v>
+        <v>184</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>1501</v>
-      </c>
-      <c r="L225" s="1" t="s">
-        <v>1523</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="226" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="15" t="s">
-        <v>1170</v>
+        <v>17</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C226" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
+      </c>
+      <c r="D226" s="27" t="s">
+        <v>1530</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>1542</v>
+        <v>1501</v>
+      </c>
+      <c r="L226" s="1" t="s">
+        <v>1523</v>
       </c>
     </row>
     <row r="227" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="15" t="s">
-        <v>40</v>
+        <v>1170</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C227" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K227" s="1" t="s">
         <v>1542</v>
       </c>
     </row>
-    <row r="228" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="16" t="s">
+    <row r="228" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B228" s="15" t="s">
+        <v>936</v>
+      </c>
+      <c r="C228" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="229" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B228" s="16" t="s">
+      <c r="B229" s="16" t="s">
         <v>1374</v>
       </c>
-      <c r="C228" s="22" t="s">
+      <c r="C229" s="22" t="s">
         <v>1371</v>
       </c>
-      <c r="G228" s="6"/>
-      <c r="L228" s="3" t="s">
+      <c r="G229" s="6"/>
+      <c r="L229" s="3" t="s">
         <v>1541</v>
-      </c>
-    </row>
-    <row r="229" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="15" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B229" s="15" t="s">
-        <v>1375</v>
-      </c>
-      <c r="C229" s="20" t="s">
-        <v>1372</v>
-      </c>
-      <c r="K229" s="1" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="230" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="15" t="s">
-        <v>17</v>
+        <v>1339</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C230" s="15" t="s">
-        <v>1373</v>
+        <v>1375</v>
+      </c>
+      <c r="C230" s="20" t="s">
+        <v>1372</v>
       </c>
       <c r="K230" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="L230" s="1" t="s">
+    </row>
+    <row r="231" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B231" s="15" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C231" s="15" t="s">
+        <v>1373</v>
+      </c>
+      <c r="K231" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L231" s="1" t="s">
         <v>1377</v>
       </c>
     </row>
-    <row r="231" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="18" t="s">
+    <row r="232" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B231" s="21"/>
-      <c r="C231" s="21"/>
-    </row>
-    <row r="232" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="15" t="s">
+      <c r="B232" s="21"/>
+      <c r="C232" s="21"/>
+    </row>
+    <row r="233" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B232" s="15" t="s">
+      <c r="B233" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C232" s="15" t="s">
+      <c r="C233" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="O232" s="1" t="s">
+      <c r="O233" s="1" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="233" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="26" t="s">
+    <row r="234" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B233" s="26" t="s">
+      <c r="B234" s="26" t="s">
         <v>1263</v>
       </c>
-      <c r="C233" s="26" t="s">
+      <c r="C234" s="26" t="s">
         <v>1264</v>
       </c>
-      <c r="T233" s="8" t="s">
+      <c r="T234" s="8" t="s">
         <v>1291</v>
       </c>
     </row>
-    <row r="234" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="16" t="s">
+    <row r="235" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B234" s="16" t="s">
+      <c r="B235" s="16" t="s">
         <v>1512</v>
       </c>
-      <c r="C234" s="16" t="s">
+      <c r="C235" s="16" t="s">
         <v>1513</v>
       </c>
-      <c r="L234" s="6" t="s">
+      <c r="L235" s="6" t="s">
         <v>1540</v>
-      </c>
-    </row>
-    <row r="235" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B235" s="15" t="s">
-        <v>937</v>
-      </c>
-      <c r="C235" s="15" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="236" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="15" t="s">
-        <v>1230</v>
+        <v>10</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>1245</v>
+        <v>937</v>
       </c>
       <c r="C236" s="15" t="s">
-        <v>1412</v>
+        <v>148</v>
       </c>
     </row>
     <row r="237" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="15" t="s">
-        <v>28</v>
+        <v>1230</v>
       </c>
       <c r="B237" s="15" t="s">
-        <v>938</v>
+        <v>1245</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>1518</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="N237" s="1" t="s">
-        <v>150</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="238" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9377,31 +9383,41 @@
         <v>28</v>
       </c>
       <c r="B238" s="15" t="s">
+        <v>938</v>
+      </c>
+      <c r="C238" s="15" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="N238" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="239" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B239" s="15" t="s">
         <v>939</v>
       </c>
-      <c r="C238" s="15" t="s">
+      <c r="C239" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="G238" s="12" t="s">
+      <c r="G239" s="12" t="s">
         <v>1285</v>
       </c>
-      <c r="N238" s="1" t="s">
+      <c r="N239" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="239" spans="1:20" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="18" t="s">
+    <row r="240" spans="1:20" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B239" s="18"/>
-      <c r="C239" s="18"/>
-    </row>
-    <row r="240" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B240" s="26"/>
-      <c r="C240" s="26"/>
+      <c r="B240" s="18"/>
+      <c r="C240" s="18"/>
     </row>
     <row r="241" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="26" t="s">
@@ -9412,30 +9428,26 @@
     </row>
     <row r="242" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B242" s="26"/>
+      <c r="C242" s="26"/>
+    </row>
+    <row r="243" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B242" s="26" t="s">
+      <c r="B243" s="26" t="s">
         <v>818</v>
       </c>
-      <c r="C242" s="26" t="s">
+      <c r="C243" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="L242" s="8" t="s">
+      <c r="L243" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T242" s="8" t="s">
+      <c r="T243" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="243" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B243" s="15" t="s">
-        <v>940</v>
-      </c>
-      <c r="C243" s="15" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="244" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9443,38 +9455,32 @@
         <v>10</v>
       </c>
       <c r="B244" s="15" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C244" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="245" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="15" t="s">
-        <v>1172</v>
+        <v>10</v>
       </c>
       <c r="B245" s="15" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="C245" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="K245" s="1" t="s">
-        <v>1542</v>
+        <v>192</v>
       </c>
     </row>
     <row r="246" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="15" t="s">
-        <v>17</v>
+        <v>1172</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K246" s="1" t="s">
         <v>1542</v>
@@ -9485,19 +9491,16 @@
         <v>17</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C247" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D247" s="27" t="s">
-        <v>1536</v>
+        <v>194</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>1544</v>
-      </c>
-      <c r="M247" s="1" t="s">
-        <v>1524</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="248" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9505,15 +9508,14 @@
         <v>17</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="C248" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D248" s="27" t="s">
-        <v>1531</v>
-      </c>
-      <c r="J248" s="27"/>
+        <v>1536</v>
+      </c>
       <c r="K248" s="1" t="s">
         <v>1544</v>
       </c>
@@ -9526,10 +9528,10 @@
         <v>17</v>
       </c>
       <c r="B249" s="15" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C249" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D249" s="27" t="s">
         <v>1531</v>
@@ -9544,23 +9546,23 @@
     </row>
     <row r="250" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="15" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B250" s="15" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C250" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D250" s="27" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="J250" s="27"/>
       <c r="K250" s="1" t="s">
         <v>1544</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="251" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9568,20 +9570,20 @@
         <v>40</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C251" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D251" s="27" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="J251" s="27"/>
       <c r="K251" s="1" t="s">
         <v>1544</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="252" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9589,45 +9591,52 @@
         <v>40</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C252" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D252" s="27" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="J252" s="27"/>
       <c r="K252" s="1" t="s">
         <v>1544</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="253" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="15" t="s">
-        <v>1174</v>
+        <v>40</v>
       </c>
       <c r="B253" s="15" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C253" s="15" t="s">
-        <v>202</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="D253" s="27" t="s">
+        <v>1534</v>
+      </c>
+      <c r="J253" s="27"/>
       <c r="K253" s="1" t="s">
-        <v>1542</v>
+        <v>1544</v>
+      </c>
+      <c r="M253" s="1" t="s">
+        <v>1527</v>
       </c>
     </row>
     <row r="254" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="15" t="s">
-        <v>40</v>
+        <v>1174</v>
       </c>
       <c r="B254" s="15" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C254" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K254" s="1" t="s">
         <v>1542</v>
@@ -9635,165 +9644,162 @@
     </row>
     <row r="255" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="15" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="B255" s="15" t="s">
-        <v>204</v>
+        <v>948</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="O255" s="1" t="s">
-        <v>1220</v>
+        <v>203</v>
+      </c>
+      <c r="K255" s="1" t="s">
+        <v>1542</v>
       </c>
     </row>
     <row r="256" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="15" t="s">
-        <v>1077</v>
+        <v>162</v>
       </c>
       <c r="B256" s="15" t="s">
-        <v>952</v>
+        <v>204</v>
       </c>
       <c r="C256" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="K256" s="1" t="s">
-        <v>1542</v>
+        <v>204</v>
+      </c>
+      <c r="O256" s="1" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="257" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="15" t="s">
-        <v>17</v>
+        <v>1077</v>
       </c>
       <c r="B257" s="15" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C257" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="D257" s="27" t="s">
-        <v>1535</v>
-      </c>
-      <c r="J257" s="27"/>
+        <v>205</v>
+      </c>
       <c r="K257" s="1" t="s">
-        <v>1544</v>
-      </c>
-      <c r="M257" s="1" t="s">
-        <v>1528</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="258" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B258" s="15" t="s">
+        <v>953</v>
+      </c>
+      <c r="C258" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D258" s="27" t="s">
+        <v>1535</v>
+      </c>
+      <c r="J258" s="27"/>
+      <c r="K258" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="M258" s="1" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="259" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B258" s="15" t="s">
+      <c r="B259" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="O258" s="1" t="s">
+      <c r="O259" s="1" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="259" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="16" t="s">
+    <row r="260" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B259" s="16" t="s">
+      <c r="B260" s="16" t="s">
         <v>1362</v>
       </c>
-      <c r="C259" s="22" t="s">
+      <c r="C260" s="22" t="s">
         <v>1367</v>
       </c>
-      <c r="G259" s="6"/>
-      <c r="L259" s="3" t="s">
+      <c r="G260" s="6"/>
+      <c r="L260" s="3" t="s">
         <v>1541</v>
-      </c>
-    </row>
-    <row r="260" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="15" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B260" s="15" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C260" s="20" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="261" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="15" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B261" s="15" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C261" s="20" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="262" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B261" s="15" t="s">
+      <c r="B262" s="15" t="s">
         <v>1364</v>
       </c>
-      <c r="C261" s="15" t="s">
+      <c r="C262" s="15" t="s">
         <v>1365</v>
       </c>
-      <c r="M261" s="1" t="s">
+      <c r="M262" s="1" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="262" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="18" t="s">
+    <row r="263" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B262" s="21"/>
-      <c r="C262" s="21"/>
-    </row>
-    <row r="263" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="26" t="s">
+      <c r="B263" s="21"/>
+      <c r="C263" s="21"/>
+    </row>
+    <row r="264" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B263" s="26" t="s">
+      <c r="B264" s="26" t="s">
         <v>1248</v>
       </c>
-      <c r="C263" s="26" t="s">
+      <c r="C264" s="26" t="s">
         <v>1247</v>
       </c>
-      <c r="L263" s="8" t="s">
+      <c r="L264" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T263" s="8" t="s">
+      <c r="T264" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="264" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B264" s="15" t="s">
-        <v>954</v>
-      </c>
-      <c r="C264" s="15" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="265" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="15" t="s">
-        <v>1230</v>
+        <v>10</v>
       </c>
       <c r="B265" s="15" t="s">
-        <v>1246</v>
+        <v>954</v>
       </c>
       <c r="C265" s="15" t="s">
-        <v>1411</v>
+        <v>148</v>
       </c>
     </row>
     <row r="266" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="15" t="s">
-        <v>28</v>
+        <v>1230</v>
       </c>
       <c r="B266" s="15" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="C266" s="15" t="s">
-        <v>1519</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="N266" s="1" t="s">
-        <v>150</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="267" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9801,24 +9807,34 @@
         <v>28</v>
       </c>
       <c r="B267" s="15" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C267" s="15" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="N267" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="268" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B268" s="15" t="s">
         <v>1242</v>
       </c>
-      <c r="C267" s="15" t="s">
+      <c r="C268" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="G267" s="1" t="s">
+      <c r="G268" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="N267" s="1" t="s">
+      <c r="N268" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="268" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B268" s="26"/>
-      <c r="C268" s="26"/>
     </row>
     <row r="269" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="26" t="s">
@@ -9829,30 +9845,26 @@
     </row>
     <row r="270" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B270" s="26"/>
+      <c r="C270" s="26"/>
+    </row>
+    <row r="271" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B270" s="26" t="s">
+      <c r="B271" s="26" t="s">
         <v>819</v>
       </c>
-      <c r="C270" s="26" t="s">
+      <c r="C271" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="L270" s="8" t="s">
+      <c r="L271" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T270" s="8" t="s">
+      <c r="T271" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="271" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B271" s="15" t="s">
-        <v>955</v>
-      </c>
-      <c r="C271" s="15" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="272" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9860,38 +9872,35 @@
         <v>10</v>
       </c>
       <c r="B272" s="15" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C272" s="15" t="s">
-        <v>1408</v>
+        <v>210</v>
       </c>
     </row>
     <row r="273" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="15" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B273" s="15" t="s">
-        <v>1194</v>
+        <v>956</v>
       </c>
       <c r="C273" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K273" s="1" t="s">
-        <v>1542</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="274" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="15" t="s">
-        <v>1175</v>
+        <v>17</v>
       </c>
       <c r="B274" s="15" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C274" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="K274" s="1" t="s">
         <v>1542</v>
@@ -9899,13 +9908,13 @@
     </row>
     <row r="275" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="15" t="s">
-        <v>40</v>
+        <v>1175</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C275" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K275" s="1" t="s">
         <v>1542</v>
@@ -9913,119 +9922,116 @@
     </row>
     <row r="276" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B276" s="15" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C276" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="K276" s="1" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="277" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B276" s="15" t="s">
+      <c r="B277" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C276" s="15" t="s">
+      <c r="C277" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="O276" s="1" t="s">
+      <c r="O277" s="1" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="277" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="16" t="s">
+    <row r="278" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B277" s="16" t="s">
+      <c r="B278" s="16" t="s">
         <v>1378</v>
       </c>
-      <c r="C277" s="22" t="s">
+      <c r="C278" s="22" t="s">
         <v>1381</v>
       </c>
-      <c r="G277" s="6"/>
-      <c r="L277" s="3" t="s">
+      <c r="G278" s="6"/>
+      <c r="L278" s="3" t="s">
         <v>1541</v>
-      </c>
-    </row>
-    <row r="278" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="15" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B278" s="15" t="s">
-        <v>1379</v>
-      </c>
-      <c r="C278" s="20" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="279" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="15" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B279" s="15" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C279" s="20" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="280" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B279" s="15" t="s">
+      <c r="B280" s="15" t="s">
         <v>1380</v>
       </c>
-      <c r="C279" s="15" t="s">
+      <c r="C280" s="15" t="s">
         <v>1383</v>
       </c>
-      <c r="L279" s="1" t="s">
+      <c r="L280" s="1" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="280" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="18" t="s">
+    <row r="281" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B280" s="21"/>
-      <c r="C280" s="21"/>
-    </row>
-    <row r="281" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="26" t="s">
+      <c r="B281" s="21"/>
+      <c r="C281" s="21"/>
+    </row>
+    <row r="282" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B281" s="26" t="s">
+      <c r="B282" s="26" t="s">
         <v>1250</v>
       </c>
-      <c r="C281" s="26" t="s">
+      <c r="C282" s="26" t="s">
         <v>1249</v>
       </c>
-      <c r="L281" s="8" t="s">
+      <c r="L282" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="T281" s="8" t="s">
+      <c r="T282" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="282" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B282" s="15" t="s">
-        <v>957</v>
-      </c>
-      <c r="C282" s="15" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="283" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="15" t="s">
-        <v>1230</v>
+        <v>10</v>
       </c>
       <c r="B283" s="15" t="s">
-        <v>1243</v>
+        <v>957</v>
       </c>
       <c r="C283" s="15" t="s">
-        <v>1412</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="284" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="15" t="s">
-        <v>28</v>
+        <v>1230</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>958</v>
+        <v>1243</v>
       </c>
       <c r="C284" s="15" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="N284" s="1" t="s">
-        <v>150</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="285" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10033,24 +10039,34 @@
         <v>28</v>
       </c>
       <c r="B285" s="15" t="s">
+        <v>958</v>
+      </c>
+      <c r="C285" s="15" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="N285" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="286" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B286" s="15" t="s">
         <v>959</v>
       </c>
-      <c r="C285" s="15" t="s">
+      <c r="C286" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="G285" s="1" t="s">
+      <c r="G286" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="N285" s="1" t="s">
+      <c r="N286" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="286" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B286" s="26"/>
-      <c r="C286" s="26"/>
     </row>
     <row r="287" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="26" t="s">
@@ -10059,52 +10075,48 @@
       <c r="B287" s="26"/>
       <c r="C287" s="26"/>
     </row>
-    <row r="288" spans="1:20" s="14" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="25" t="s">
+    <row r="288" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="26" t="s">
         <v>1334</v>
       </c>
-      <c r="B288" s="25"/>
-      <c r="C288" s="25"/>
-    </row>
-    <row r="289" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="18" t="s">
+      <c r="B288" s="26"/>
+      <c r="C288" s="26"/>
+    </row>
+    <row r="289" spans="1:20" s="14" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="25" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B289" s="25"/>
+      <c r="C289" s="25"/>
+    </row>
+    <row r="290" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B289" s="21"/>
-      <c r="C289" s="21"/>
-    </row>
-    <row r="290" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="26" t="s">
+      <c r="B290" s="21"/>
+      <c r="C290" s="21"/>
+    </row>
+    <row r="291" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B290" s="26" t="s">
+      <c r="B291" s="26" t="s">
         <v>1267</v>
       </c>
-      <c r="C290" s="23" t="s">
+      <c r="C291" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="D290" s="8" t="s">
+      <c r="D291" s="8" t="s">
         <v>1479</v>
       </c>
-      <c r="G290" s="8" t="s">
+      <c r="G291" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="L290" s="8" t="s">
+      <c r="L291" s="8" t="s">
         <v>1444</v>
       </c>
-      <c r="T290" s="8" t="s">
+      <c r="T291" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="291" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B291" s="15" t="s">
-        <v>960</v>
-      </c>
-      <c r="C291" s="15" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="292" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10112,44 +10124,38 @@
         <v>10</v>
       </c>
       <c r="B292" s="15" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C292" s="15" t="s">
-        <v>1406</v>
+        <v>218</v>
       </c>
     </row>
     <row r="293" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="15" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B293" s="15" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C293" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="H293" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="I293" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K293" s="1" t="s">
-        <v>1444</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="294" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="15" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B294" s="15" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
+      </c>
+      <c r="H294" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I294" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="K294" s="1" t="s">
         <v>1444</v>
@@ -10157,27 +10163,30 @@
     </row>
     <row r="295" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="15" t="s">
-        <v>1175</v>
+        <v>17</v>
       </c>
       <c r="B295" s="15" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C295" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>1506</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="296" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="15" t="s">
-        <v>40</v>
+        <v>1175</v>
       </c>
       <c r="B296" s="15" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C296" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K296" s="1" t="s">
         <v>1506</v>
@@ -10185,167 +10194,164 @@
     </row>
     <row r="297" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="15" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="B297" s="15" t="s">
-        <v>226</v>
+        <v>965</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="O297" s="1" t="s">
-        <v>1222</v>
+        <v>225</v>
+      </c>
+      <c r="K297" s="1" t="s">
+        <v>1506</v>
       </c>
     </row>
     <row r="298" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="15" t="s">
-        <v>1077</v>
+        <v>162</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>966</v>
+        <v>226</v>
       </c>
       <c r="C298" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="K298" s="1" t="s">
-        <v>1506</v>
+        <v>226</v>
+      </c>
+      <c r="O298" s="1" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="299" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="15" t="s">
-        <v>40</v>
+        <v>1077</v>
       </c>
       <c r="B299" s="15" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C299" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K299" s="1" t="s">
-        <v>1444</v>
-      </c>
-      <c r="M299" s="1" t="s">
-        <v>1068</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="300" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B300" s="15" t="s">
+        <v>967</v>
+      </c>
+      <c r="C300" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="K300" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="M300" s="1" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="301" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B300" s="15" t="s">
+      <c r="B301" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C300" s="15" t="s">
+      <c r="C301" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="O300" s="1" t="s">
+      <c r="O301" s="1" t="s">
         <v>1223</v>
       </c>
     </row>
-    <row r="301" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="16" t="s">
+    <row r="302" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B301" s="16" t="s">
+      <c r="B302" s="16" t="s">
         <v>1386</v>
       </c>
-      <c r="C301" s="22" t="s">
+      <c r="C302" s="22" t="s">
         <v>1430</v>
       </c>
-      <c r="G301" s="6"/>
-      <c r="M301" s="3" t="s">
+      <c r="G302" s="6"/>
+      <c r="M302" s="3" t="s">
         <v>1501</v>
-      </c>
-    </row>
-    <row r="302" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="15" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B302" s="15" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C302" s="20" t="s">
-        <v>1385</v>
-      </c>
-      <c r="K302" s="1" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="303" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="15" t="s">
-        <v>17</v>
+        <v>1339</v>
       </c>
       <c r="B303" s="15" t="s">
-        <v>1388</v>
-      </c>
-      <c r="C303" s="15" t="s">
-        <v>1384</v>
+        <v>1387</v>
+      </c>
+      <c r="C303" s="20" t="s">
+        <v>1385</v>
       </c>
       <c r="K303" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="M303" s="1" t="s">
+    </row>
+    <row r="304" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A304" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B304" s="15" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C304" s="15" t="s">
+        <v>1384</v>
+      </c>
+      <c r="K304" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="M304" s="1" t="s">
         <v>1389</v>
       </c>
     </row>
-    <row r="304" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="18" t="s">
+    <row r="305" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B304" s="21"/>
-      <c r="C304" s="21"/>
-    </row>
-    <row r="305" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="26" t="s">
+      <c r="B305" s="21"/>
+      <c r="C305" s="21"/>
+    </row>
+    <row r="306" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A306" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B305" s="26" t="s">
+      <c r="B306" s="26" t="s">
         <v>1252</v>
       </c>
-      <c r="C305" s="26" t="s">
+      <c r="C306" s="26" t="s">
         <v>1251</v>
       </c>
-      <c r="T305" s="8" t="s">
+      <c r="T306" s="8" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="306" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A306" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B306" s="15" t="s">
-        <v>968</v>
-      </c>
-      <c r="C306" s="15" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="307" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="15" t="s">
-        <v>1230</v>
+        <v>10</v>
       </c>
       <c r="B307" s="15" t="s">
-        <v>1244</v>
+        <v>968</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>1412</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="308" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="15" t="s">
-        <v>28</v>
+        <v>1230</v>
       </c>
       <c r="B308" s="15" t="s">
-        <v>1266</v>
+        <v>1244</v>
       </c>
       <c r="C308" s="15" t="s">
-        <v>1521</v>
-      </c>
-      <c r="G308" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="N308" s="1" t="s">
-        <v>150</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="309" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10353,24 +10359,34 @@
         <v>28</v>
       </c>
       <c r="B309" s="15" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C309" s="15" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="N309" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="310" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A310" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B310" s="15" t="s">
         <v>1200</v>
       </c>
-      <c r="C309" s="15" t="s">
+      <c r="C310" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="G309" s="1" t="s">
+      <c r="G310" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="N309" s="1" t="s">
+      <c r="N310" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="310" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B310" s="26"/>
-      <c r="C310" s="26"/>
     </row>
     <row r="311" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="26" t="s">
@@ -10379,37 +10395,30 @@
       <c r="B311" s="26"/>
       <c r="C311" s="26"/>
     </row>
-    <row r="312" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A312" s="16" t="s">
+    <row r="312" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B312" s="26"/>
+      <c r="C312" s="26"/>
+    </row>
+    <row r="313" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A313" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B312" s="16" t="s">
+      <c r="B313" s="16" t="s">
         <v>820</v>
       </c>
-      <c r="C312" s="23" t="s">
+      <c r="C313" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="D312" s="6" t="s">
+      <c r="D313" s="6" t="s">
         <v>1480</v>
       </c>
-      <c r="G312" s="6" t="s">
+      <c r="G313" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="L312" s="6" t="s">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="313" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A313" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="B313" s="15" t="s">
-        <v>969</v>
-      </c>
-      <c r="C313" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="K313" s="1" t="s">
+      <c r="L313" s="6" t="s">
         <v>1444</v>
       </c>
     </row>
@@ -10418,10 +10427,10 @@
         <v>232</v>
       </c>
       <c r="B314" s="15" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C314" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K314" s="1" t="s">
         <v>1444</v>
@@ -10432,10 +10441,10 @@
         <v>232</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K315" s="1" t="s">
         <v>1444</v>
@@ -10446,10 +10455,10 @@
         <v>232</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C316" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K316" s="1" t="s">
         <v>1444</v>
@@ -10460,10 +10469,10 @@
         <v>232</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K317" s="1" t="s">
         <v>1444</v>
@@ -10474,10 +10483,10 @@
         <v>232</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K318" s="1" t="s">
         <v>1444</v>
@@ -10488,96 +10497,96 @@
         <v>232</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C319" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K319" s="1" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="320" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A320" s="18" t="s">
+    <row r="320" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B320" s="15" t="s">
+        <v>975</v>
+      </c>
+      <c r="C320" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="K320" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B320" s="21"/>
-      <c r="C320" s="21"/>
-    </row>
-    <row r="321" spans="1:15" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A321" s="16" t="s">
+      <c r="B321" s="21"/>
+      <c r="C321" s="21"/>
+    </row>
+    <row r="322" spans="1:15" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B321" s="16" t="s">
+      <c r="B322" s="16" t="s">
         <v>821</v>
       </c>
-      <c r="C321" s="16" t="s">
+      <c r="C322" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="D321" s="6" t="s">
+      <c r="D322" s="6" t="s">
         <v>1481</v>
       </c>
-      <c r="G321" s="6" t="s">
+      <c r="G322" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="L321" s="6" t="s">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="322" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A322" s="15" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B322" s="15" t="s">
-        <v>980</v>
-      </c>
-      <c r="C322" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="K322" s="1" t="s">
+      <c r="L322" s="6" t="s">
         <v>1444</v>
       </c>
     </row>
     <row r="323" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="15" t="s">
-        <v>17</v>
+        <v>1197</v>
       </c>
       <c r="B323" s="15" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C323" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K323" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="M323" s="1" t="s">
-        <v>1069</v>
-      </c>
     </row>
     <row r="324" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="15" t="s">
-        <v>1177</v>
+        <v>17</v>
       </c>
       <c r="B324" s="15" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C324" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K324" s="1" t="s">
         <v>1444</v>
       </c>
+      <c r="M324" s="1" t="s">
+        <v>1069</v>
+      </c>
     </row>
     <row r="325" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="15" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B325" s="15" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C325" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K325" s="1" t="s">
         <v>1444</v>
@@ -10585,13 +10594,13 @@
     </row>
     <row r="326" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="15" t="s">
-        <v>40</v>
+        <v>1179</v>
       </c>
       <c r="B326" s="15" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C326" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K326" s="1" t="s">
         <v>1444</v>
@@ -10599,56 +10608,56 @@
     </row>
     <row r="327" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B327" s="15" t="s">
+        <v>979</v>
+      </c>
+      <c r="C327" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="K327" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B327" s="15" t="s">
+      <c r="B328" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C327" s="15" t="s">
+      <c r="C328" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="O327" s="1" t="s">
+      <c r="O328" s="1" t="s">
         <v>1224</v>
       </c>
     </row>
-    <row r="328" spans="1:15" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A328" s="18" t="s">
+    <row r="329" spans="1:15" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B328" s="21"/>
-      <c r="C328" s="21"/>
-    </row>
-    <row r="329" spans="1:15" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A329" s="16" t="s">
+      <c r="B329" s="21"/>
+      <c r="C329" s="21"/>
+    </row>
+    <row r="330" spans="1:15" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B329" s="16" t="s">
+      <c r="B330" s="16" t="s">
         <v>986</v>
       </c>
-      <c r="C329" s="16" t="s">
+      <c r="C330" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="D329" s="6" t="s">
+      <c r="D330" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="G329" s="6" t="s">
+      <c r="G330" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="L329" s="6" t="s">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="330" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="15" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B330" s="15" t="s">
-        <v>981</v>
-      </c>
-      <c r="C330" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="K330" s="1" t="s">
+      <c r="L330" s="6" t="s">
         <v>1444</v>
       </c>
     </row>
@@ -10657,10 +10666,10 @@
         <v>1077</v>
       </c>
       <c r="B331" s="15" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C331" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K331" s="1" t="s">
         <v>1444</v>
@@ -10671,13 +10680,10 @@
         <v>1077</v>
       </c>
       <c r="B332" s="15" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C332" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K332" s="1" t="s">
         <v>1444</v>
@@ -10685,67 +10691,67 @@
     </row>
     <row r="333" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="15" t="s">
-        <v>232</v>
+        <v>1077</v>
       </c>
       <c r="B333" s="15" t="s">
-        <v>1201</v>
+        <v>983</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K333" s="1" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="334" spans="1:15" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A334" s="16" t="s">
+    <row r="334" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B334" s="15" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C334" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K334" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B334" s="16" t="s">
+      <c r="B335" s="16" t="s">
         <v>985</v>
       </c>
-      <c r="C334" s="16" t="s">
+      <c r="C335" s="16" t="s">
         <v>1225</v>
       </c>
-      <c r="D334" s="6" t="s">
+      <c r="D335" s="6" t="s">
         <v>1226</v>
       </c>
-      <c r="L334" s="6" t="s">
+      <c r="L335" s="6" t="s">
         <v>1444</v>
-      </c>
-    </row>
-    <row r="335" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A335" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B335" s="15" t="s">
-        <v>984</v>
-      </c>
-      <c r="C335" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="336" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="15" t="s">
-        <v>1182</v>
+        <v>10</v>
       </c>
       <c r="B336" s="15" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C336" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="G336" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I336" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="337" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10753,16 +10759,13 @@
         <v>1182</v>
       </c>
       <c r="B337" s="15" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C337" s="15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="H337" s="1" t="s">
-        <v>1268</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>258</v>
@@ -10773,16 +10776,16 @@
         <v>1182</v>
       </c>
       <c r="B338" s="15" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C338" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>259</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>258</v>
@@ -10793,16 +10796,16 @@
         <v>1182</v>
       </c>
       <c r="B339" s="15" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>259</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>258</v>
@@ -10813,16 +10816,16 @@
         <v>1182</v>
       </c>
       <c r="B340" s="15" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C340" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>259</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>258</v>
@@ -10830,27 +10833,33 @@
     </row>
     <row r="341" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="15" t="s">
-        <v>1077</v>
+        <v>1182</v>
       </c>
       <c r="B341" s="15" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C341" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="K341" s="1" t="s">
-        <v>1444</v>
+        <v>263</v>
+      </c>
+      <c r="G341" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H341" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="342" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="15" t="s">
-        <v>17</v>
+        <v>1077</v>
       </c>
       <c r="B342" s="15" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K342" s="1" t="s">
         <v>1444</v>
@@ -10861,10 +10870,10 @@
         <v>17</v>
       </c>
       <c r="B343" s="15" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C343" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K343" s="1" t="s">
         <v>1444</v>
@@ -10875,10 +10884,10 @@
         <v>17</v>
       </c>
       <c r="B344" s="15" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C344" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K344" s="1" t="s">
         <v>1444</v>
@@ -10886,13 +10895,13 @@
     </row>
     <row r="345" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="15" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B345" s="15" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C345" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K345" s="1" t="s">
         <v>1444</v>
@@ -10903,10 +10912,10 @@
         <v>40</v>
       </c>
       <c r="B346" s="15" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C346" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K346" s="1" t="s">
         <v>1444</v>
@@ -10914,27 +10923,34 @@
     </row>
     <row r="347" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="15" t="s">
-        <v>1184</v>
+        <v>40</v>
       </c>
       <c r="B347" s="15" t="s">
-        <v>1202</v>
+        <v>997</v>
       </c>
       <c r="C347" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K347" s="1" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="348" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="18" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B348" s="21"/>
-      <c r="C348" s="21"/>
+    <row r="348" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="15" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B348" s="15" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C348" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K348" s="1" t="s">
+        <v>1444</v>
+      </c>
     </row>
     <row r="349" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="18" t="s">
@@ -10943,49 +10959,42 @@
       <c r="B349" s="21"/>
       <c r="C349" s="21"/>
     </row>
-    <row r="350" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="16" t="s">
+    <row r="350" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="18" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B350" s="21"/>
+      <c r="C350" s="21"/>
+    </row>
+    <row r="351" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B350" s="16" t="s">
+      <c r="B351" s="16" t="s">
         <v>822</v>
       </c>
-      <c r="C350" s="16" t="s">
+      <c r="C351" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="D350" s="6" t="s">
+      <c r="D351" s="6" t="s">
         <v>1483</v>
       </c>
-      <c r="G350" s="6" t="s">
+      <c r="G351" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="L350" s="6" t="s">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="351" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B351" s="15" t="s">
-        <v>998</v>
-      </c>
-      <c r="C351" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="K351" s="1" t="s">
+      <c r="L351" s="6" t="s">
         <v>1444</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="15" t="s">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="B352" s="15" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C352" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K352" s="1" t="s">
         <v>1444</v>
@@ -10993,54 +11002,57 @@
     </row>
     <row r="353" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="15" t="s">
-        <v>40</v>
+        <v>232</v>
       </c>
       <c r="B353" s="15" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C353" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K353" s="1" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="354" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="18" t="s">
+    <row r="354" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B354" s="15" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C354" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="K354" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B354" s="21"/>
-      <c r="C354" s="21"/>
-    </row>
-    <row r="355" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="16" t="s">
+      <c r="B355" s="21"/>
+      <c r="C355" s="21"/>
+    </row>
+    <row r="356" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B355" s="16" t="s">
+      <c r="B356" s="16" t="s">
         <v>1203</v>
       </c>
-      <c r="C355" s="16" t="s">
+      <c r="C356" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="D355" s="6" t="s">
+      <c r="D356" s="6" t="s">
         <v>1484</v>
       </c>
-      <c r="G355" s="6" t="s">
+      <c r="G356" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="L355" s="6" t="s">
+      <c r="L356" s="6" t="s">
         <v>1444</v>
-      </c>
-    </row>
-    <row r="356" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B356" s="15" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C356" s="15" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="357" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11048,10 +11060,10 @@
         <v>10</v>
       </c>
       <c r="B357" s="15" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="358" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11059,27 +11071,21 @@
         <v>10</v>
       </c>
       <c r="B358" s="15" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C358" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="359" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="15" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B359" s="15" t="s">
-        <v>1001</v>
+        <v>1021</v>
       </c>
       <c r="C359" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G359" s="1" t="s">
-        <v>1390</v>
+        <v>279</v>
       </c>
     </row>
     <row r="360" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11087,10 +11093,10 @@
         <v>28</v>
       </c>
       <c r="B360" s="15" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C360" s="15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>281</v>
@@ -11099,32 +11105,32 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="361" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A361" s="16" t="s">
+    <row r="361" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B361" s="15" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C361" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G361" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B361" s="16" t="s">
+      <c r="B362" s="16" t="s">
         <v>824</v>
       </c>
-      <c r="C361" s="16" t="s">
+      <c r="C362" s="16" t="s">
         <v>283</v>
-      </c>
-    </row>
-    <row r="362" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A362" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B362" s="15" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C362" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="D362" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G362" s="1" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="363" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11132,10 +11138,10 @@
         <v>28</v>
       </c>
       <c r="B363" s="15" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C363" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>281</v>
@@ -11144,42 +11150,39 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="364" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="18" t="s">
+    <row r="364" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B364" s="15" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C364" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G364" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B364" s="21"/>
-      <c r="C364" s="21"/>
-    </row>
-    <row r="365" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A365" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B365" s="15" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C365" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G365" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="L365" s="1" t="s">
-        <v>1444</v>
-      </c>
+      <c r="B365" s="21"/>
+      <c r="C365" s="21"/>
     </row>
     <row r="366" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="15" t="s">
         <v>28</v>
       </c>
       <c r="B366" s="15" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C366" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>281</v>
@@ -11196,10 +11199,10 @@
         <v>28</v>
       </c>
       <c r="B367" s="15" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C367" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>281</v>
@@ -11211,35 +11214,38 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="368" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A368" s="16" t="s">
+    <row r="368" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B368" s="15" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C368" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G368" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="L368" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A369" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B368" s="16" t="s">
+      <c r="B369" s="16" t="s">
         <v>825</v>
       </c>
-      <c r="C368" s="16" t="s">
+      <c r="C369" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="L368" s="6" t="s">
+      <c r="L369" s="6" t="s">
         <v>1444</v>
-      </c>
-    </row>
-    <row r="369" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B369" s="15" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C369" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="D369" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G369" s="1" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="370" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11247,10 +11253,10 @@
         <v>28</v>
       </c>
       <c r="B370" s="15" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C370" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>281</v>
@@ -11259,42 +11265,42 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="371" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="18" t="s">
+    <row r="371" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B371" s="15" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C371" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G371" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B371" s="21"/>
-      <c r="C371" s="21"/>
-    </row>
-    <row r="372" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="16" t="s">
+      <c r="B372" s="21"/>
+      <c r="C372" s="21"/>
+    </row>
+    <row r="373" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B372" s="16" t="s">
+      <c r="B373" s="16" t="s">
         <v>826</v>
       </c>
-      <c r="C372" s="16" t="s">
+      <c r="C373" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="L372" s="6" t="s">
+      <c r="L373" s="6" t="s">
         <v>1444</v>
-      </c>
-    </row>
-    <row r="373" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B373" s="15" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C373" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="D373" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G373" s="1" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="374" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11302,10 +11308,10 @@
         <v>28</v>
       </c>
       <c r="B374" s="15" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C374" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>281</v>
@@ -11314,62 +11320,62 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="375" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A375" s="18" t="s">
+    <row r="375" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B375" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C375" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G375" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B375" s="21"/>
-      <c r="C375" s="21"/>
-    </row>
-    <row r="376" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A376" s="15" t="s">
+      <c r="B376" s="21"/>
+      <c r="C376" s="21"/>
+    </row>
+    <row r="377" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B376" s="15" t="s">
+      <c r="B377" s="15" t="s">
         <v>1012</v>
       </c>
-      <c r="C376" s="15" t="s">
+      <c r="C377" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="D376" s="1" t="s">
+      <c r="D377" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G376" s="1" t="s">
+      <c r="G377" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="L376" s="1" t="s">
+      <c r="L377" s="1" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="377" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="16" t="s">
+    <row r="378" spans="1:12" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B377" s="16" t="s">
+      <c r="B378" s="16" t="s">
         <v>827</v>
       </c>
-      <c r="C377" s="16" t="s">
+      <c r="C378" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="L377" s="6" t="s">
+      <c r="L378" s="6" t="s">
         <v>1444</v>
-      </c>
-    </row>
-    <row r="378" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A378" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B378" s="15" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C378" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G378" s="1" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="379" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11377,10 +11383,10 @@
         <v>28</v>
       </c>
       <c r="B379" s="15" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C379" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>281</v>
@@ -11394,10 +11400,10 @@
         <v>28</v>
       </c>
       <c r="B380" s="15" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C380" s="15" t="s">
-        <v>1471</v>
+        <v>298</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>281</v>
@@ -11406,42 +11412,39 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="381" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="18" t="s">
+    <row r="381" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B381" s="15" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C381" s="15" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G381" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A382" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B381" s="21"/>
-      <c r="C381" s="21"/>
-    </row>
-    <row r="382" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B382" s="15" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C382" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="D382" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G382" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="L382" s="1" t="s">
-        <v>1444</v>
-      </c>
+      <c r="B382" s="21"/>
+      <c r="C382" s="21"/>
     </row>
     <row r="383" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="15" t="s">
         <v>28</v>
       </c>
       <c r="B383" s="15" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C383" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>281</v>
@@ -11458,10 +11461,10 @@
         <v>28</v>
       </c>
       <c r="B384" s="15" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C384" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>281</v>
@@ -11473,42 +11476,51 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="385" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="18" t="s">
+    <row r="385" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B385" s="15" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C385" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G385" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="L385" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="386" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B385" s="21"/>
-      <c r="C385" s="21"/>
-    </row>
-    <row r="386" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A386" s="16" t="s">
+      <c r="B386" s="21"/>
+      <c r="C386" s="21"/>
+    </row>
+    <row r="387" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B386" s="16" t="s">
+      <c r="B387" s="16" t="s">
         <v>823</v>
       </c>
-      <c r="C386" s="16" t="s">
+      <c r="C387" s="16" t="s">
         <v>1407</v>
       </c>
-      <c r="D386" s="6" t="s">
+      <c r="D387" s="6" t="s">
         <v>1485</v>
       </c>
-      <c r="G386" s="6" t="s">
+      <c r="G387" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="L386" s="6" t="s">
+      <c r="L387" s="6" t="s">
         <v>1444</v>
-      </c>
-    </row>
-    <row r="387" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A387" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B387" s="15" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C387" s="15" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="388" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11516,10 +11528,10 @@
         <v>10</v>
       </c>
       <c r="B388" s="15" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C388" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="389" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11527,10 +11539,10 @@
         <v>10</v>
       </c>
       <c r="B389" s="15" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C389" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="390" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11538,115 +11550,112 @@
         <v>10</v>
       </c>
       <c r="B390" s="15" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C390" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="391" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A391" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B391" s="15" t="s">
         <v>1025</v>
       </c>
-      <c r="C390" s="15" t="s">
+      <c r="C391" s="15" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="391" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A391" s="26" t="s">
+    <row r="392" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A392" s="26" t="s">
         <v>1335</v>
       </c>
-      <c r="B391" s="26" t="s">
+      <c r="B392" s="26" t="s">
         <v>1026</v>
       </c>
-      <c r="C391" s="26" t="s">
+      <c r="C392" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="D391" s="8" t="s">
+      <c r="D392" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="L391" s="8" t="s">
+      <c r="L392" s="8" t="s">
         <v>1444</v>
       </c>
-      <c r="T391" s="8" t="s">
+      <c r="T392" s="8" t="s">
         <v>1291</v>
       </c>
     </row>
-    <row r="392" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A392" s="15" t="s">
+    <row r="393" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B392" s="15" t="s">
+      <c r="B393" s="15" t="s">
         <v>1027</v>
       </c>
-      <c r="C392" s="15" t="s">
+      <c r="C393" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="D392" s="1" t="s">
+      <c r="D393" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="G392" s="1" t="s">
+      <c r="G393" s="1" t="s">
         <v>1390</v>
       </c>
     </row>
-    <row r="393" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A393" s="26" t="s">
+    <row r="394" spans="1:20" s="8" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A394" s="26" t="s">
         <v>1334</v>
       </c>
-      <c r="B393" s="26"/>
-      <c r="C393" s="26"/>
-    </row>
-    <row r="394" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A394" s="18" t="s">
+      <c r="B394" s="26"/>
+      <c r="C394" s="26"/>
+    </row>
+    <row r="395" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A395" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B394" s="21"/>
-      <c r="C394" s="21"/>
-    </row>
-    <row r="395" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A395" s="16" t="s">
-        <v>1332</v>
-      </c>
-      <c r="B395" s="16" t="s">
-        <v>1490</v>
-      </c>
-      <c r="C395" s="16" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D395" s="6" t="s">
-        <v>1486</v>
-      </c>
-      <c r="G395" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L395" s="6" t="s">
-        <v>1444</v>
-      </c>
+      <c r="B395" s="21"/>
+      <c r="C395" s="21"/>
     </row>
     <row r="396" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="16" t="s">
         <v>1332</v>
       </c>
       <c r="B396" s="16" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C396" s="16" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D396" s="6" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G396" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L396" s="6" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="397" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A397" s="16" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B397" s="16" t="s">
         <v>1433</v>
       </c>
-      <c r="C396" s="16" t="s">
+      <c r="C397" s="16" t="s">
         <v>1431</v>
       </c>
-      <c r="L396" s="6" t="s">
+      <c r="L397" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="M396" s="6" t="s">
+      <c r="M397" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="T396" s="6" t="s">
+      <c r="T397" s="6" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="397" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A397" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B397" s="15" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C397" s="15" t="s">
-        <v>1448</v>
-      </c>
-      <c r="G397" s="1" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="398" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11654,10 +11663,10 @@
         <v>149</v>
       </c>
       <c r="B398" s="15" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="C398" s="15" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>1390</v>
@@ -11668,10 +11677,10 @@
         <v>149</v>
       </c>
       <c r="B399" s="15" t="s">
-        <v>1449</v>
+        <v>1429</v>
       </c>
       <c r="C399" s="15" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>1390</v>
@@ -11682,10 +11691,10 @@
         <v>149</v>
       </c>
       <c r="B400" s="15" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="C400" s="15" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>1390</v>
@@ -11696,10 +11705,10 @@
         <v>149</v>
       </c>
       <c r="B401" s="15" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="C401" s="15" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>1390</v>
@@ -11710,10 +11719,10 @@
         <v>149</v>
       </c>
       <c r="B402" s="15" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C402" s="15" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>1390</v>
@@ -11724,122 +11733,119 @@
         <v>149</v>
       </c>
       <c r="B403" s="15" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C403" s="15" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>1390</v>
       </c>
     </row>
-    <row r="404" spans="1:20" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A404" s="18" t="s">
+    <row r="404" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A404" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B404" s="15" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C404" s="15" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G404" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="405" spans="1:20" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A405" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B404" s="18" t="s">
+      <c r="B405" s="18" t="s">
         <v>1432</v>
       </c>
-      <c r="C404" s="18"/>
-    </row>
-    <row r="405" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A405" s="16" t="s">
+      <c r="C405" s="18"/>
+    </row>
+    <row r="406" spans="1:20" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A406" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B405" s="16" t="s">
+      <c r="B406" s="16" t="s">
         <v>1487</v>
       </c>
-      <c r="C405" s="16" t="s">
+      <c r="C406" s="16" t="s">
         <v>1489</v>
       </c>
-      <c r="L405" s="6" t="s">
+      <c r="L406" s="6" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="406" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A406" s="15" t="s">
+    <row r="407" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B406" s="15" t="s">
+      <c r="B407" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="C406" s="15" t="s">
+      <c r="C407" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="D406" s="1" t="s">
+      <c r="D407" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="K406" s="1" t="s">
+      <c r="K407" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="L406" s="1" t="s">
+      <c r="L407" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="M406" s="1" t="s">
+      <c r="M407" s="1" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="407" spans="1:20" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A407" s="18" t="s">
+    <row r="408" spans="1:20" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A408" s="18" t="s">
         <v>1333</v>
       </c>
-      <c r="B407" s="18"/>
-      <c r="C407" s="18"/>
-    </row>
-    <row r="408" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A408" s="16" t="s">
+      <c r="B408" s="18"/>
+      <c r="C408" s="18"/>
+    </row>
+    <row r="409" spans="1:20" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A409" s="16" t="s">
         <v>1332</v>
       </c>
-      <c r="B408" s="16" t="s">
+      <c r="B409" s="16" t="s">
         <v>1397</v>
       </c>
-      <c r="C408" s="22" t="s">
+      <c r="C409" s="22" t="s">
         <v>1393</v>
       </c>
-      <c r="G408" s="6"/>
-      <c r="L408" s="6" t="s">
+      <c r="G409" s="6"/>
+      <c r="L409" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="T408" s="3" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="409" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A409" s="15" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B409" s="15" t="s">
-        <v>1391</v>
-      </c>
-      <c r="C409" s="20" t="s">
-        <v>1394</v>
-      </c>
-      <c r="F409" s="11"/>
-      <c r="K409" s="1" t="s">
-        <v>1444</v>
-      </c>
-      <c r="O409" s="11" t="s">
-        <v>1399</v>
-      </c>
-      <c r="P409" s="11"/>
-      <c r="Q409" s="11"/>
-      <c r="T409" s="1" t="s">
+      <c r="T409" s="3" t="s">
         <v>1291</v>
       </c>
     </row>
     <row r="410" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="15" t="s">
-        <v>17</v>
+        <v>1339</v>
       </c>
       <c r="B410" s="15" t="s">
-        <v>1392</v>
-      </c>
-      <c r="C410" s="15" t="s">
-        <v>1395</v>
-      </c>
-      <c r="G410" s="12" t="s">
-        <v>1285</v>
-      </c>
+        <v>1391</v>
+      </c>
+      <c r="C410" s="20" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F410" s="11"/>
+      <c r="K410" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="O410" s="11" t="s">
+        <v>1399</v>
+      </c>
+      <c r="P410" s="11"/>
+      <c r="Q410" s="11"/>
       <c r="T410" s="1" t="s">
         <v>1291</v>
       </c>
@@ -11849,27 +11855,37 @@
         <v>17</v>
       </c>
       <c r="B411" s="15" t="s">
-        <v>1507</v>
+        <v>1392</v>
       </c>
       <c r="C411" s="15" t="s">
         <v>1395</v>
       </c>
-      <c r="K411" s="1" t="s">
+      <c r="G411" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="T411" s="1" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="412" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A412" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B412" s="15" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C412" s="15" t="s">
+        <v>1395</v>
+      </c>
+      <c r="K412" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="L411" s="1" t="s">
+      <c r="L412" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="S411" s="1">
+      <c r="S412" s="1">
         <v>3000</v>
       </c>
-    </row>
-    <row r="412" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A412" s="18" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B412" s="21"/>
-      <c r="C412" s="21"/>
     </row>
     <row r="413" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="18" t="s">
@@ -11878,14 +11894,21 @@
       <c r="B413" s="21"/>
       <c r="C413" s="21"/>
     </row>
+    <row r="414" spans="1:20" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A414" s="18" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B414" s="21"/>
+      <c r="C414" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W413" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:W414" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
     <dataValidation type="custom" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Name" error="Question names:_x000a__x000a_• Must be unique_x000a_• Must start with a letter_x000a_• Can only contain letters, numbers and underscores_x000a_• Cannot contain reserved keywords or special characters_x000a_• Cannot exceed 31 characters (ArcGIS Enterprise)" sqref="B8 B6:C7" xr:uid="{DC482C0F-926E-4D2E-A0D9-6B9D179CA6A1}">
       <formula1>AND(ISERR(LEFT(B6,1)*1),LEN(B6)=LEN(SUBSTITUTE(B6," ","")),LEN(B6)&lt;32,COUNTIF(survay_S,B6)=0,SUMPRODUCT(--ISNUMBER(SEARCH(SpecialChars,B6)))=0)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G59:G67 G73:G77 G410 G238 G4:G15 G18:G23 G115" xr:uid="{C3EE3982-9C4E-4E59-9A6F-EA26C585FD2B}">
+    <dataValidation type="list" allowBlank="1" sqref="G59:G67 G73:G77 G411 G239 G4:G15 G18:G23 G115 G119" xr:uid="{C3EE3982-9C4E-4E59-9A6F-EA26C585FD2B}">
       <formula1>IF(LEFT(C4,4)="rank",aRank,IF(LEFT(C4,16)="select_multiple ",aSM,IF(LEFT(C4,11)="select_one ",aSO,IF(LEFT(C4,12)="select_one_f",aSOF,IF(LEFT(C4,17)="select_multiple_f",aSMF,IF(C4="begin group",aGrp,IF(C4="begin repeat",aRpt,INDIRECT("a"&amp;C4))))))))</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="A13 A6:A11" xr:uid="{53BF0EB8-F11F-4A5D-8755-909A4DE218C5}">
